--- a/GDPR_map.xlsx
+++ b/GDPR_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/filippo/Documents/UIC/Tesi UIC/automated-software-analysis for privacy policy compliance/GDPR_navigator_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC3FEF5-C541-294B-B99F-94FF92F980DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20AA4D46-21E2-EA49-AD39-C06227C6723F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="6000" windowWidth="28800" windowHeight="15940" xr2:uid="{3DC3CFF2-E72D-FB46-B327-1564F4C8CC32}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{3DC3CFF2-E72D-FB46-B327-1564F4C8CC32}"/>
   </bookViews>
   <sheets>
     <sheet name="Cartel1" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="971">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="972">
   <si>
     <t>Article</t>
   </si>
@@ -3000,6 +3000,9 @@
   </si>
   <si>
     <t>Article 93(3)</t>
+  </si>
+  <si>
+    <t>Art. 6(1)(a)</t>
   </si>
 </sst>
 </file>
@@ -4147,7 +4150,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>55</v>
+        <v>971</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>56</v>
